--- a/data/Varna_ReSources_Input.xlsx
+++ b/data/Varna_ReSources_Input.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/petermarshall/Desktop/Varna-Slides/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/petermarshall/Desktop/Github/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{466728FB-BAA5-E64A-9006-4465E7A81381}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03689EE4-8E3B-1F47-998F-553256ED8125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3180" yWindow="4060" windowWidth="23040" windowHeight="12460" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3180" yWindow="4060" windowWidth="23040" windowHeight="12460" tabRatio="500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="consumer" sheetId="1" r:id="rId1"/>
@@ -2134,52 +2134,28 @@
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="1">
-        <v>-24</v>
-      </c>
-      <c r="C2" s="1">
-        <v>0.7</v>
-      </c>
-      <c r="D2" s="1">
-        <v>4</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1.8</v>
-      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="1">
-        <v>-20.399999999999999</v>
-      </c>
-      <c r="C3" s="1">
-        <v>1.4</v>
-      </c>
-      <c r="D3" s="1">
-        <v>6.3</v>
-      </c>
-      <c r="E3" s="1">
-        <v>1.7</v>
-      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B4" s="1">
-        <v>-18.7</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0.1</v>
-      </c>
-      <c r="D4" s="1">
-        <v>12.7</v>
-      </c>
-      <c r="E4" s="1">
-        <v>0.1</v>
-      </c>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
@@ -2244,19 +2220,19 @@
       </c>
       <c r="B3" s="4">
         <f>source_data!B2-2</f>
-        <v>-26</v>
+        <v>-2</v>
       </c>
       <c r="C3" s="4">
         <f>CEILING(source_data!C2,0.5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D3" s="4">
         <f>source_data!B2+0.5</f>
-        <v>-23.5</v>
+        <v>0.5</v>
       </c>
       <c r="E3" s="4">
         <f>CEILING(source_data!E2,0.5)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4"/>
@@ -2265,11 +2241,11 @@
       </c>
       <c r="I3" s="4">
         <f>source_data!D2</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4">
         <f>CEILING(source_data!E2,0.5)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -2278,19 +2254,19 @@
       </c>
       <c r="B4" s="4">
         <f>source_data!B3-2</f>
-        <v>-22.4</v>
+        <v>-2</v>
       </c>
       <c r="C4" s="4">
         <f>CEILING(source_data!C3,0.5)</f>
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="D4" s="4">
         <f>source_data!B3-8</f>
-        <v>-28.4</v>
+        <v>-8</v>
       </c>
       <c r="E4" s="4">
         <f>CEILING(source_data!E3,0.5)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4"/>
@@ -2299,11 +2275,11 @@
       </c>
       <c r="I4" s="4">
         <f>source_data!D3</f>
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4">
         <f>CEILING(source_data!E3,0.5)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -2312,19 +2288,19 @@
       </c>
       <c r="B5" s="4">
         <f>source_data!B4-1</f>
-        <v>-19.7</v>
+        <v>-1</v>
       </c>
       <c r="C5" s="4">
         <f>CEILING(source_data!C4,0.5)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D5" s="4">
         <f>source_data!B4-7</f>
-        <v>-25.7</v>
+        <v>-7</v>
       </c>
       <c r="E5" s="4">
         <f>CEILING(source_data!E4,0.5)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
@@ -2333,11 +2309,11 @@
       </c>
       <c r="I5" s="4">
         <f>source_data!D4+1.5</f>
-        <v>14.2</v>
+        <v>1.5</v>
       </c>
       <c r="J5" s="4">
         <f>CEILING(source_data!E4,0.5)</f>
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
